--- a/Apostas_Diarias/Apostas_20260405.xlsx
+++ b/Apostas_Diarias/Apostas_20260405.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_2B590F4F95C6C57D4DC0CAF0507960B06AAFF538" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02FA1C5A-E1A7-4468-891B-DB90E7ED2AC6}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_2B590F4F9596453385E0C2F050C0E03676C5E9B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FCFE97F-F5BB-4DC4-98BB-97FF45B6D314}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
   <si>
     <t>Data</t>
   </si>
@@ -74,34 +74,106 @@
     <t>P1 ⭐</t>
   </si>
   <si>
+    <t>08:35:00</t>
+  </si>
+  <si>
+    <t>CHINA 1</t>
+  </si>
+  <si>
+    <t>Tianjin Jinmen Tiger FC x Shanghai Shenhua</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>SWEDEN 1</t>
+  </si>
+  <si>
+    <t>Kalmar FF x Vasteras SK</t>
+  </si>
+  <si>
     <t>10:00:00</t>
   </si>
   <si>
+    <t>SWEDEN 2</t>
+  </si>
+  <si>
+    <t>Sundsvall x United IK Nordic</t>
+  </si>
+  <si>
     <t>ITALY 1</t>
   </si>
   <si>
     <t>US Cremonese x Bologna</t>
   </si>
   <si>
-    <t>Lay_CS_0x1_B365</t>
-  </si>
-  <si>
-    <t>10:30:00</t>
-  </si>
-  <si>
-    <t>GERMANY 1</t>
-  </si>
-  <si>
-    <t>Union Berlin x St Pauli</t>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>SERBIA 1</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica x Crvena Zvezda</t>
+  </si>
+  <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>SCOTLAND 1</t>
+  </si>
+  <si>
+    <t>Dundee x Celtic</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>ISRAEL 1</t>
+  </si>
+  <si>
+    <t>Hapoel Haifa x Maccabi Tel Aviv</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>BRAZIL 1</t>
+  </si>
+  <si>
+    <t>Chapecoense x EC Vitoria Salvador</t>
+  </si>
+  <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
+    <t>Bahia x SE Palmeiras</t>
+  </si>
+  <si>
+    <t>Corinthians x Internacional</t>
   </si>
   <si>
     <t>P2</t>
   </si>
   <si>
+    <t>Livingston x Hearts</t>
+  </si>
+  <si>
     <t>13:00:00</t>
   </si>
   <si>
     <t>Pisa x Torino</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>CHILE 1</t>
+  </si>
+  <si>
+    <t>Deportes Concepcion x Colo Colo</t>
   </si>
 </sst>
 </file>
@@ -441,14 +513,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -491,6 +563,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -512,12 +587,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <f>G2</f>
+        <v>10.5</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -526,7 +603,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>54.360465116279073</v>
+        <v>49.210526315789473</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -552,24 +629,26 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="H3">
-        <v>12.5</v>
+        <f t="shared" ref="H3:H14" si="0">G3</f>
+        <v>11.5</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I14" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J4" si="0">IF(L3=1,"GREEN","RED")</f>
-        <v>GREEN</v>
+        <f t="shared" ref="J3:J14" si="2">IF(L3=1,"GREEN","RED")</f>
+        <v>RED</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K4" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>40.652173913043484</v>
+        <f t="shared" ref="K3:K14" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>-500</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -577,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
@@ -592,24 +671,446 @@
         <v>16</v>
       </c>
       <c r="G4">
+        <v>11.5</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>9.6</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>9.6</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="3"/>
+        <v>54.360465116279073</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>46.75</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>11.5</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>10.5</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>46.75</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>11.5</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>11.5</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="2"/>
+        <v>RED</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>-500</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>59.935897435897431</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13">
         <v>8.6</v>
       </c>
-      <c r="H4">
+      <c r="H13">
+        <f t="shared" si="0"/>
         <v>8.6</v>
       </c>
-      <c r="I4">
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="2"/>
+        <v>RED</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>-500</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H14">
         <f t="shared" si="0"/>
-        <v>RED</v>
-      </c>
-      <c r="K4">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I14">
         <f t="shared" si="1"/>
-        <v>-500</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="3"/>
+        <v>59.935897435897431</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Apostas_Diarias/Apostas_20260405.xlsx
+++ b/Apostas_Diarias/Apostas_20260405.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_2B590F4F9596453385E0C2F050C0E03676C5E9B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FCFE97F-F5BB-4DC4-98BB-97FF45B6D314}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_08F18C579586C515E5E3D5F0505ED87656CD2B05" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63BBBF80-F68D-492F-93B5-CE1E5C33524E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="68">
   <si>
     <t>Data</t>
   </si>
@@ -74,6 +74,21 @@
     <t>P1 ⭐</t>
   </si>
   <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>TURKEY 1</t>
+  </si>
+  <si>
+    <t>Fatih Karagumruk Istanbul x Rizespor</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
+    <t>Samsunspor x Konyaspor</t>
+  </si>
+  <si>
     <t>08:35:00</t>
   </si>
   <si>
@@ -83,16 +98,13 @@
     <t>Tianjin Jinmen Tiger FC x Shanghai Shenhua</t>
   </si>
   <si>
-    <t>Lay_CS_0x1_B365</t>
-  </si>
-  <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
-    <t>SWEDEN 1</t>
-  </si>
-  <si>
-    <t>Kalmar FF x Vasteras SK</t>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>NETHERLANDS 1</t>
+  </si>
+  <si>
+    <t>FC Volendam x Feyenoord</t>
   </si>
   <si>
     <t>10:00:00</t>
@@ -101,45 +113,87 @@
     <t>SWEDEN 2</t>
   </si>
   <si>
+    <t>Norrby IF x IK Brage</t>
+  </si>
+  <si>
+    <t>TURKEY 2</t>
+  </si>
+  <si>
+    <t>Sivasspor x Erokspor A.S</t>
+  </si>
+  <si>
     <t>Sundsvall x United IK Nordic</t>
   </si>
   <si>
-    <t>ITALY 1</t>
-  </si>
-  <si>
-    <t>US Cremonese x Bologna</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>SERBIA 1</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica x Crvena Zvezda</t>
-  </si>
-  <si>
-    <t>12:30:00</t>
-  </si>
-  <si>
-    <t>SCOTLAND 1</t>
-  </si>
-  <si>
-    <t>Dundee x Celtic</t>
-  </si>
-  <si>
-    <t>14:15:00</t>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>CZECH 1</t>
+  </si>
+  <si>
+    <t>Banik Ostrava x Slavia Prague</t>
+  </si>
+  <si>
+    <t>GERMANY 1</t>
+  </si>
+  <si>
+    <t>Union Berlin x St Pauli</t>
+  </si>
+  <si>
+    <t>11:15:00</t>
+  </si>
+  <si>
+    <t>SPAIN 1</t>
+  </si>
+  <si>
+    <t>Valencia x Celta Vigo</t>
+  </si>
+  <si>
+    <t>12:15:00</t>
+  </si>
+  <si>
+    <t>FRANCE 1</t>
+  </si>
+  <si>
+    <t>Le Havre x Auxerre</t>
+  </si>
+  <si>
+    <t>Lorient x Paris FC</t>
+  </si>
+  <si>
+    <t>Metz x Nantes</t>
+  </si>
+  <si>
+    <t>12:55:00</t>
+  </si>
+  <si>
+    <t>SAUDI ARABIA 1</t>
+  </si>
+  <si>
+    <t>Al-Akhdoud x Al-Fateh (KSA)</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
   </si>
   <si>
     <t>ISRAEL 1</t>
   </si>
   <si>
-    <t>Hapoel Haifa x Maccabi Tel Aviv</t>
+    <t>FC Ashdod x Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>Al Riyadh SC x Al-Shabab (KSA)</t>
   </si>
   <si>
     <t>16:00:00</t>
   </si>
   <si>
+    <t>Alaves x Osasuna</t>
+  </si>
+  <si>
     <t>BRAZIL 1</t>
   </si>
   <si>
@@ -158,13 +212,13 @@
     <t>P2</t>
   </si>
   <si>
-    <t>Livingston x Hearts</t>
-  </si>
-  <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>Pisa x Torino</t>
+    <t>Angers x Lyon</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>Oviedo x Sevilla</t>
   </si>
   <si>
     <t>16:30:00</t>
@@ -174,6 +228,15 @@
   </si>
   <si>
     <t>Deportes Concepcion x Colo Colo</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Lay_CS_1x0_B365</t>
+  </si>
+  <si>
+    <t>P4</t>
   </si>
 </sst>
 </file>
@@ -513,13 +576,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -563,9 +626,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -575,26 +635,24 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -603,7 +661,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>49.210526315789473</v>
+        <v>42.5</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -617,13 +675,13 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -632,23 +690,21 @@
         <v>11.5</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H14" si="0">G3</f>
         <v>11.5</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I14" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J14" si="2">IF(L3=1,"GREEN","RED")</f>
-        <v>RED</v>
+        <f t="shared" ref="J3:J38" si="0">IF(L3=1,"GREEN","RED")</f>
+        <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K14" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>-500</v>
+        <f t="shared" ref="K3:K38" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>44.523809523809526</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -659,35 +715,33 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>11.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I4">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <f t="shared" si="1"/>
+        <v>53.125</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -698,38 +752,36 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H5">
-        <f t="shared" si="0"/>
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I5">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K5">
-        <f t="shared" si="3"/>
-        <v>54.360465116279073</v>
+        <f t="shared" si="1"/>
+        <v>55.654761904761905</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -740,38 +792,36 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K6">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <f t="shared" si="1"/>
+        <v>61.513157894736842</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -785,13 +835,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -800,19 +850,17 @@
         <v>11.5</v>
       </c>
       <c r="H7">
-        <f t="shared" si="0"/>
         <v>11.5</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>44.523809523809526</v>
       </c>
       <c r="L7">
@@ -824,37 +872,35 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>10.5</v>
       </c>
       <c r="H8">
-        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>49.210526315789473</v>
       </c>
       <c r="L8">
@@ -869,35 +915,33 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K9">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <f t="shared" si="1"/>
+        <v>51.944444444444443</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -911,35 +955,33 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H10">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I10">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K10">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <f t="shared" si="1"/>
+        <v>46.75</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -950,41 +992,39 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G11">
-        <v>11.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="H11">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I11">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J11" t="str">
-        <f t="shared" si="2"/>
-        <v>RED</v>
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K11">
-        <f t="shared" si="3"/>
-        <v>-500</v>
+        <f t="shared" si="1"/>
+        <v>53.125</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -992,41 +1032,39 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12">
-        <v>8.8000000000000007</v>
+        <v>11.5</v>
       </c>
       <c r="H12">
-        <f t="shared" si="0"/>
-        <v>8.8000000000000007</v>
+        <v>11.5</v>
       </c>
       <c r="I12">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J12" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
+        <f t="shared" si="0"/>
+        <v>RED</v>
       </c>
       <c r="K12">
-        <f t="shared" si="3"/>
-        <v>59.935897435897431</v>
+        <f t="shared" si="1"/>
+        <v>-500</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1034,41 +1072,39 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="H13">
-        <f t="shared" si="0"/>
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="I13">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J13" t="str">
-        <f t="shared" si="2"/>
-        <v>RED</v>
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
       </c>
       <c r="K13">
-        <f t="shared" si="3"/>
-        <v>-500</v>
+        <f t="shared" si="1"/>
+        <v>73.046875</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1076,16 +1112,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -1094,26 +1130,987 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="H14">
-        <f t="shared" si="0"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="I14">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J14" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
+        <f t="shared" si="0"/>
+        <v>RED</v>
       </c>
       <c r="K14">
-        <f t="shared" si="3"/>
-        <v>59.935897435897431</v>
+        <f t="shared" si="1"/>
+        <v>-500</v>
       </c>
       <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>13</v>
+      </c>
+      <c r="I15">
+        <v>500</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>38.958333333333336</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+      <c r="H16">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>500</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>35.96153846153846</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>15</v>
+      </c>
+      <c r="H17">
+        <v>15</v>
+      </c>
+      <c r="I17">
+        <v>500</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>33.392857142857146</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18">
+        <v>11.5</v>
+      </c>
+      <c r="H18">
+        <v>11.5</v>
+      </c>
+      <c r="I18">
+        <v>500</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="H19">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I19">
+        <v>500</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>53.125</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20">
+        <v>8.4</v>
+      </c>
+      <c r="H20">
+        <v>8.4</v>
+      </c>
+      <c r="I20">
+        <v>500</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>63.175675675675684</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21">
+        <v>11.5</v>
+      </c>
+      <c r="H21">
+        <v>11.5</v>
+      </c>
+      <c r="I21">
+        <v>500</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22">
+        <v>9.6</v>
+      </c>
+      <c r="H22">
+        <v>9.6</v>
+      </c>
+      <c r="I22">
+        <v>500</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>54.360465116279073</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23">
+        <v>9.6</v>
+      </c>
+      <c r="H23">
+        <v>9.6</v>
+      </c>
+      <c r="I23">
+        <v>500</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>54.360465116279073</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24">
+        <v>11</v>
+      </c>
+      <c r="H24">
+        <v>11</v>
+      </c>
+      <c r="I24">
+        <v>500</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>46.75</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25">
+        <v>12</v>
+      </c>
+      <c r="H25">
+        <v>12</v>
+      </c>
+      <c r="I25">
+        <v>500</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>13</v>
+      </c>
+      <c r="I26">
+        <v>500</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>38.958333333333336</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27">
+        <v>8.4</v>
+      </c>
+      <c r="H27">
+        <v>8.4</v>
+      </c>
+      <c r="I27">
+        <v>500</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>63.175675675675684</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H28">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I28">
+        <v>500</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29">
+        <v>13.5</v>
+      </c>
+      <c r="H29">
+        <v>13.5</v>
+      </c>
+      <c r="I29">
+        <v>500</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>37.400000000000006</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30">
+        <v>10.5</v>
+      </c>
+      <c r="H30">
+        <v>10.5</v>
+      </c>
+      <c r="I30">
+        <v>500</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31">
+        <v>12</v>
+      </c>
+      <c r="H31">
+        <v>12</v>
+      </c>
+      <c r="I31">
+        <v>500</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32">
+        <v>11.5</v>
+      </c>
+      <c r="H32">
+        <v>11.5</v>
+      </c>
+      <c r="I32">
+        <v>500</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="H33">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I33">
+        <v>500</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>53.125</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34">
+        <v>10.5</v>
+      </c>
+      <c r="H34">
+        <v>10.5</v>
+      </c>
+      <c r="I34">
+        <v>500</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35">
+        <v>12.5</v>
+      </c>
+      <c r="H35">
+        <v>12.5</v>
+      </c>
+      <c r="I35">
+        <v>500</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>40.652173913043484</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36">
+        <v>7.2</v>
+      </c>
+      <c r="H36">
+        <v>7.2</v>
+      </c>
+      <c r="I36">
+        <v>500</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>75.403225806451616</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37">
+        <v>10.5</v>
+      </c>
+      <c r="H37">
+        <v>10.5</v>
+      </c>
+      <c r="I37">
+        <v>500</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" t="s">
+        <v>66</v>
+      </c>
+      <c r="G38">
+        <v>8.6</v>
+      </c>
+      <c r="H38">
+        <v>8.6</v>
+      </c>
+      <c r="I38">
+        <v>500</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>61.513157894736842</v>
+      </c>
+      <c r="L38">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K38">
+    <sortCondition ref="E2:E38"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>